--- a/artfynd/A 65586-2021 artfynd.xlsx
+++ b/artfynd/A 65586-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65586-2021 artfynd.xlsx
+++ b/artfynd/A 65586-2021 artfynd.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Detta är tredje gången vi sett en lappuggla på vår tomt, dom stannar ofta en god stund, flera timmar. Men sista fotot som finns är från våren 2019. Tidigare gånger vi sett lappugglor har det varit vinter.</t>
+          <t>Detta är tredje gången vi sett en lappuggla på vår tomt, dom stannar ofta en god stund, flera timmar. Men sista fotot som finns ä</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 65586-2021 artfynd.xlsx
+++ b/artfynd/A 65586-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>99081706</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597372.4198480212</v>
+        <v>597372</v>
       </c>
       <c r="R2" t="n">
-        <v>7170992.86192446</v>
+        <v>7170992</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,19 +754,9 @@
           <t>2017-02-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-02-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -806,12 +791,7 @@
         <v>99082219</v>
       </c>
       <c r="B3" t="n">
-        <v>56366</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -854,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597372.4198480212</v>
+        <v>597372</v>
       </c>
       <c r="R3" t="n">
-        <v>7170992.86192446</v>
+        <v>7170992</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,19 +867,9 @@
           <t>2019-05-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-05-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
